--- a/Minnesota_Timberwolves_2025-26_stats.xlsx
+++ b/Minnesota_Timberwolves_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,120 @@
         <v>27</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>11</v>
+      </c>
+      <c r="P13" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>26</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>19</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1161,7 +1275,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1875,6 +1989,120 @@
         <v>7</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1889,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2603,6 +2831,120 @@
         <v>8</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>12</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2617,7 +2959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:Q14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3331,6 +3673,120 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
+        <v>4</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3367,7 +3823,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.14285714285714</v>
+        <v>27.33333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3377,7 +3833,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25.36363636363636</v>
+        <v>25.46153846153846</v>
       </c>
     </row>
     <row r="4">
@@ -3387,7 +3843,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.36363636363636</v>
+        <v>17.69230769230769</v>
       </c>
     </row>
     <row r="5">
@@ -3397,27 +3853,27 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.81818181818182</v>
+        <v>14.07692307692308</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rudy Gobert</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.90909090909091</v>
+        <v>11.53846153846154</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Rudy Gobert</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.81818181818182</v>
+        <v>10.38461538461539</v>
       </c>
     </row>
     <row r="8">
@@ -3427,27 +3883,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.363636363636363</v>
+        <v>6.230769230769231</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rob Dillingham</t>
+          <t>Jaylen Clark</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.333333333333333</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jaylen Clark</t>
+          <t>Rob Dillingham</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.222222222222222</v>
+        <v>4.636363636363637</v>
       </c>
     </row>
     <row r="11">
@@ -3457,7 +3913,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.7</v>
+        <v>4.272727272727272</v>
       </c>
     </row>
     <row r="12">
@@ -3477,7 +3933,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.333333333333333</v>
+        <v>2.142857142857143</v>
       </c>
     </row>
     <row r="14">
@@ -3487,7 +3943,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.714285714285714</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="15">
@@ -3497,7 +3953,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -3543,17 +3999,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.181818181818182</v>
+        <v>6.230769230769231</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mike Conley</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.727272727272727</v>
+        <v>3.666666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -3563,33 +4019,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.636363636363636</v>
+        <v>3.538461538461538</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Mike Conley</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.285714285714286</v>
+        <v>3.538461538461538</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Rob Dillingham</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.333333333333333</v>
+        <v>2.307692307692307</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Rob Dillingham</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3603,7 +4059,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.818181818181818</v>
+        <v>2.076923076923077</v>
       </c>
     </row>
     <row r="9">
@@ -3613,7 +4069,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.5</v>
+        <v>1.363636363636364</v>
       </c>
     </row>
     <row r="10">
@@ -3623,7 +4079,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.454545454545455</v>
+        <v>1.307692307692308</v>
       </c>
     </row>
     <row r="11">
@@ -3653,7 +4109,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="14">
@@ -3663,7 +4119,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="15">
@@ -3673,7 +4129,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="16">
@@ -3719,7 +4175,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.09090909090909</v>
+        <v>9.615384615384615</v>
       </c>
     </row>
     <row r="3">
@@ -3729,7 +4185,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.181818181818182</v>
+        <v>7.384615384615385</v>
       </c>
     </row>
     <row r="4">
@@ -3739,27 +4195,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>5.615384615384615</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Anthony Edwards</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.636363636363637</v>
+        <v>4.555555555555555</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Anthony Edwards</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.142857142857143</v>
+        <v>4.538461538461538</v>
       </c>
     </row>
     <row r="7">
@@ -3769,7 +4225,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.545454545454545</v>
+        <v>3.846153846153846</v>
       </c>
     </row>
     <row r="8">
@@ -3789,7 +4245,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.222222222222222</v>
+        <v>2.090909090909091</v>
       </c>
     </row>
     <row r="10">
@@ -3799,7 +4255,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.181818181818182</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -3809,23 +4265,23 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.166666666666667</v>
+        <v>1.142857142857143</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Joan Beringer</t>
+          <t>Rob Dillingham</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.142857142857143</v>
+        <v>1.090909090909091</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bones Hyland</t>
+          <t>Joan Beringer</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -3835,11 +4291,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rob Dillingham</t>
+          <t>Bones Hyland</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.9090909090909091</v>
       </c>
     </row>
     <row r="15">
@@ -3849,7 +4305,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="16">
@@ -3895,7 +4351,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.142857142857143</v>
+        <v>3.333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -3905,7 +4361,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.909090909090909</v>
+        <v>2.923076923076923</v>
       </c>
     </row>
     <row r="4">
@@ -3915,27 +4371,27 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1.923076923076923</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jaden McDaniels</t>
+          <t>Naz Reid</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.909090909090909</v>
+        <v>1.846153846153846</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Naz Reid</t>
+          <t>Jaden McDaniels</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.636363636363636</v>
+        <v>1.692307692307692</v>
       </c>
     </row>
     <row r="7">
@@ -3945,7 +4401,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.363636363636364</v>
+        <v>1.384615384615385</v>
       </c>
     </row>
     <row r="8">
@@ -3955,7 +4411,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8</v>
+        <v>0.7272727272727273</v>
       </c>
     </row>
     <row r="9">
@@ -3965,7 +4421,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6363636363636364</v>
       </c>
     </row>
     <row r="10">
@@ -3985,7 +4441,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="12">
@@ -3995,7 +4451,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -4049,7 +4505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4310,6 +4766,48 @@
         <v>233</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SAC</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>124</v>
+      </c>
+      <c r="D13" t="n">
+        <v>110</v>
+      </c>
+      <c r="E13" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>112</v>
+      </c>
+      <c r="D14" t="n">
+        <v>123</v>
+      </c>
+      <c r="E14" t="n">
+        <v>235</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
